--- a/slots/resources/sample/PrivilegeCard.xlsx
+++ b/slots/resources/sample/PrivilegeCard.xlsx
@@ -192,7 +192,7 @@
     <t>1990000_20000</t>
   </si>
   <si>
-    <t>1021350_1</t>
+    <t>1031350_1</t>
   </si>
 </sst>
 </file>
@@ -1395,7 +1395,6 @@
       <c r="I7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="1"/>
       <c r="L7"/>
       <c r="M7"/>
     </row>

--- a/slots/resources/sample/PrivilegeCard.xlsx
+++ b/slots/resources/sample/PrivilegeCard.xlsx
@@ -138,7 +138,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>map&lt;int{_}long&gt;{;}</t>
+    <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
     <t>id</t>
@@ -168,28 +168,28 @@
     <t>月卡</t>
   </si>
   <si>
-    <t>1990000_300000</t>
-  </si>
-  <si>
-    <t>1990000_10000</t>
+    <t>1990000_12475000</t>
+  </si>
+  <si>
+    <t>1990000_415800</t>
   </si>
   <si>
     <t>季卡</t>
   </si>
   <si>
-    <t>1990000_1350000</t>
-  </si>
-  <si>
-    <t>1990000_15000</t>
+    <t>1990000_89970000</t>
+  </si>
+  <si>
+    <t>1990000_999700</t>
   </si>
   <si>
     <t>永久卡</t>
   </si>
   <si>
-    <t>1990000_3600000</t>
-  </si>
-  <si>
-    <t>1990000_20000</t>
+    <t>1990000_454965000</t>
+  </si>
+  <si>
+    <t>1990000_1516600</t>
   </si>
   <si>
     <t>1031350_1</t>
@@ -376,12 +376,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/slots/resources/sample/PrivilegeCard.xlsx
+++ b/slots/resources/sample/PrivilegeCard.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8532E3AE-2A5E-4F71-9893-3C1D06B1C2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PrivilegeCard" sheetId="1" r:id="rId1"/>
@@ -27,12 +33,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -56,7 +62,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -79,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -106,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
   <si>
     <t>序列ID</t>
   </si>
@@ -193,19 +199,17 @@
   </si>
   <si>
     <t>1031350_1</t>
+  </si>
+  <si>
+    <t>BigDecimal</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,7 +225,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.25"/>
+      <color theme="0" tint="-0.249977111117893"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -230,150 +234,6 @@
       <color indexed="8"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -386,8 +246,21 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -396,192 +269,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -589,255 +282,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -847,7 +298,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -859,62 +310,21 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1192,14 +602,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.25" style="1" customWidth="1"/>
@@ -1219,7 +629,7 @@
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1248,7 +658,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +672,8 @@
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>9</v>
+      <c r="F2" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -1275,7 +685,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1302,7 +712,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1313,7 +723,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1339,7 +749,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1367,7 +777,7 @@
       <c r="L6"/>
       <c r="M6"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1398,77 +808,77 @@
       <c r="L7"/>
       <c r="M7"/>
     </row>
-    <row r="8" spans="12:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="L8"/>
       <c r="M8"/>
     </row>
-    <row r="9" spans="12:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="L9"/>
       <c r="M9"/>
     </row>
-    <row r="10" spans="12:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="L10"/>
       <c r="M10"/>
     </row>
-    <row r="11" spans="12:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="L11"/>
       <c r="M11"/>
     </row>
-    <row r="12" spans="12:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="L12"/>
       <c r="M12"/>
     </row>
-    <row r="13" spans="12:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="L13"/>
       <c r="M13"/>
     </row>
-    <row r="14" spans="12:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="L14"/>
       <c r="M14"/>
     </row>
-    <row r="15" spans="12:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="L15"/>
       <c r="M15"/>
     </row>
-    <row r="16" spans="12:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="L16"/>
       <c r="M16"/>
     </row>
-    <row r="17" spans="12:13">
+    <row r="17" spans="12:13" x14ac:dyDescent="0.2">
       <c r="L17"/>
       <c r="M17"/>
     </row>
-    <row r="18" spans="12:13">
+    <row r="18" spans="12:13" x14ac:dyDescent="0.2">
       <c r="L18"/>
       <c r="M18"/>
     </row>
-    <row r="19" spans="12:13">
+    <row r="19" spans="12:13" x14ac:dyDescent="0.2">
       <c r="L19"/>
       <c r="M19"/>
     </row>
-    <row r="20" spans="12:13">
+    <row r="20" spans="12:13" x14ac:dyDescent="0.2">
       <c r="L20"/>
       <c r="M20"/>
     </row>
-    <row r="21" spans="12:13">
+    <row r="21" spans="12:13" x14ac:dyDescent="0.2">
       <c r="L21"/>
       <c r="M21"/>
     </row>
-    <row r="22" spans="12:13">
+    <row r="22" spans="12:13" x14ac:dyDescent="0.2">
       <c r="L22"/>
       <c r="M22"/>
     </row>
-    <row r="23" spans="12:13">
+    <row r="23" spans="12:13" x14ac:dyDescent="0.2">
       <c r="L23"/>
       <c r="M23"/>
     </row>
-    <row r="24" spans="12:13">
+    <row r="24" spans="12:13" x14ac:dyDescent="0.2">
       <c r="L24"/>
       <c r="M24"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/PrivilegeCard.xlsx
+++ b/slots/resources/sample/PrivilegeCard.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8532E3AE-2A5E-4F71-9893-3C1D06B1C2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="PrivilegeCard" sheetId="1" r:id="rId1"/>
@@ -33,12 +27,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -62,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -85,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -144,6 +138,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>BigDecimal</t>
+  </si>
+  <si>
     <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
@@ -199,17 +196,19 @@
   </si>
   <si>
     <t>1031350_1</t>
-  </si>
-  <si>
-    <t>BigDecimal</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -225,7 +224,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.249977111117893"/>
+      <color theme="0" tint="-0.25"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -234,6 +233,150 @@
       <color indexed="8"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -246,21 +389,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -269,12 +399,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6C6AC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -282,9 +598,266 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -298,7 +871,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -310,21 +886,62 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -602,14 +1219,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:M24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.25" style="1" customWidth="1"/>
@@ -629,7 +1246,7 @@
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -658,7 +1275,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -672,47 +1289,47 @@
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="G2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="I3" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -723,7 +1340,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -731,7 +1348,7 @@
         <v>56001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -740,16 +1357,16 @@
         <v>30</v>
       </c>
       <c r="F5" s="1">
-        <v>499</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="4" t="s">
+        <v>4.99</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="H5" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -757,7 +1374,7 @@
         <v>56002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
@@ -766,18 +1383,18 @@
         <v>90</v>
       </c>
       <c r="F6" s="1">
-        <v>2999</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="4" t="s">
+        <v>29.99</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>24</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="L6"/>
       <c r="M6"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -785,7 +1402,7 @@
         <v>56003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -794,91 +1411,91 @@
         <v>999999</v>
       </c>
       <c r="F7" s="1">
-        <v>12999</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="4" t="s">
+        <v>99.99</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>27</v>
       </c>
+      <c r="H7" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="I7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L7"/>
       <c r="M7"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="12:13">
       <c r="L8"/>
       <c r="M8"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="12:13">
       <c r="L9"/>
       <c r="M9"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="12:13">
       <c r="L10"/>
       <c r="M10"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="12:13">
       <c r="L11"/>
       <c r="M11"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="12:13">
       <c r="L12"/>
       <c r="M12"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="12:13">
       <c r="L13"/>
       <c r="M13"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="12:13">
       <c r="L14"/>
       <c r="M14"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="12:13">
       <c r="L15"/>
       <c r="M15"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="12:13">
       <c r="L16"/>
       <c r="M16"/>
     </row>
-    <row r="17" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="12:13">
       <c r="L17"/>
       <c r="M17"/>
     </row>
-    <row r="18" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="12:13">
       <c r="L18"/>
       <c r="M18"/>
     </row>
-    <row r="19" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="12:13">
       <c r="L19"/>
       <c r="M19"/>
     </row>
-    <row r="20" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="12:13">
       <c r="L20"/>
       <c r="M20"/>
     </row>
-    <row r="21" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="12:13">
       <c r="L21"/>
       <c r="M21"/>
     </row>
-    <row r="22" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="12:13">
       <c r="L22"/>
       <c r="M22"/>
     </row>
-    <row r="23" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="12:13">
       <c r="L23"/>
       <c r="M23"/>
     </row>
-    <row r="24" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="12:13">
       <c r="L24"/>
       <c r="M24"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/PrivilegeCard.xlsx
+++ b/slots/resources/sample/PrivilegeCard.xlsx
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
   <si>
     <t>序列ID</t>
   </si>
@@ -136,6 +136,9 @@
   </si>
   <si>
     <t>int</t>
+  </si>
+  <si>
+    <t>BigDecimal</t>
   </si>
   <si>
     <t>map&lt;int{_}long&gt;{|}</t>
@@ -387,7 +390,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -402,6 +405,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF6C6AC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -581,12 +590,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -713,7 +737,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -725,119 +749,119 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -845,6 +869,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -1262,44 +1289,44 @@
       <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>10</v>
+      <c r="G2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="6" t="s">
         <v>18</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1321,7 +1348,7 @@
         <v>56001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -1330,13 +1357,13 @@
         <v>30</v>
       </c>
       <c r="F5" s="1">
-        <v>499</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="4" t="s">
+        <v>4.99</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>21</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1347,7 +1374,7 @@
         <v>56002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
@@ -1356,13 +1383,13 @@
         <v>90</v>
       </c>
       <c r="F6" s="1">
-        <v>2999</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="4" t="s">
+        <v>29.99</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>24</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="L6"/>
       <c r="M6"/>
@@ -1375,7 +1402,7 @@
         <v>56003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -1384,16 +1411,16 @@
         <v>999999</v>
       </c>
       <c r="F7" s="1">
-        <v>12999</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="4" t="s">
+        <v>99.99</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>27</v>
       </c>
+      <c r="H7" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="I7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L7"/>
       <c r="M7"/>

--- a/slots/resources/sample/PrivilegeCard.xlsx
+++ b/slots/resources/sample/PrivilegeCard.xlsx
@@ -189,10 +189,10 @@
     <t>永久卡</t>
   </si>
   <si>
-    <t>1990000_454965000</t>
-  </si>
-  <si>
-    <t>1990000_1516600</t>
+    <t>1990000_349965000</t>
+  </si>
+  <si>
+    <t>1990000_1166600</t>
   </si>
   <si>
     <t>1031350_1</t>
@@ -379,12 +379,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/slots/resources/sample/PrivilegeCard.xlsx
+++ b/slots/resources/sample/PrivilegeCard.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE1D610-3E83-4D34-A1A7-CA4F8E5DDD73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PrivilegeCard" sheetId="1" r:id="rId1"/>
@@ -27,12 +33,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -56,7 +62,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -79,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -106,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
   <si>
     <t>序列ID</t>
   </si>
@@ -196,19 +202,25 @@
   </si>
   <si>
     <t>1031350_1</t>
+  </si>
+  <si>
+    <t>渠道商品ID</t>
+  </si>
+  <si>
+    <t>map&lt;int{_}String&gt;{|}</t>
+  </si>
+  <si>
+    <t>channelCommodity</t>
+  </si>
+  <si>
+    <t>1_1|2_2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,7 +236,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.25"/>
+      <color theme="0" tint="-0.249977111117893"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -233,150 +245,6 @@
       <color indexed="8"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -389,8 +257,14 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -399,7 +273,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -409,188 +283,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -613,251 +307,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -874,7 +326,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -887,61 +339,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1219,14 +627,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.25" style="1" customWidth="1"/>
@@ -1237,7 +645,7 @@
     <col min="7" max="7" width="18.875" style="1" customWidth="1"/>
     <col min="8" max="8" width="17.875" style="1" customWidth="1"/>
     <col min="9" max="9" width="23.625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.25" style="1"/>
+    <col min="10" max="10" width="21.375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9" style="1"/>
     <col min="12" max="12" width="7.875" style="1" customWidth="1"/>
     <col min="13" max="13" width="26.75" style="1" customWidth="1"/>
@@ -1246,7 +654,7 @@
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1274,8 +682,11 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -1301,8 +712,11 @@
       <c r="I2" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
+      <c r="J2" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -1328,8 +742,11 @@
       <c r="I3" s="7" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="J3" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1340,7 +757,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1365,8 +782,11 @@
       <c r="H5" s="5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="J5" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -1391,10 +811,13 @@
       <c r="H6" s="5" t="s">
         <v>25</v>
       </c>
+      <c r="J6" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="L6"/>
       <c r="M6"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1422,80 +845,83 @@
       <c r="I7" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="J7" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="L7"/>
       <c r="M7"/>
     </row>
-    <row r="8" spans="12:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="L8"/>
       <c r="M8"/>
     </row>
-    <row r="9" spans="12:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="L9"/>
       <c r="M9"/>
     </row>
-    <row r="10" spans="12:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="L10"/>
       <c r="M10"/>
     </row>
-    <row r="11" spans="12:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="L11"/>
       <c r="M11"/>
     </row>
-    <row r="12" spans="12:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="L12"/>
       <c r="M12"/>
     </row>
-    <row r="13" spans="12:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="L13"/>
       <c r="M13"/>
     </row>
-    <row r="14" spans="12:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="L14"/>
       <c r="M14"/>
     </row>
-    <row r="15" spans="12:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="L15"/>
       <c r="M15"/>
     </row>
-    <row r="16" spans="12:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="L16"/>
       <c r="M16"/>
     </row>
-    <row r="17" spans="12:13">
+    <row r="17" spans="12:13" x14ac:dyDescent="0.2">
       <c r="L17"/>
       <c r="M17"/>
     </row>
-    <row r="18" spans="12:13">
+    <row r="18" spans="12:13" x14ac:dyDescent="0.2">
       <c r="L18"/>
       <c r="M18"/>
     </row>
-    <row r="19" spans="12:13">
+    <row r="19" spans="12:13" x14ac:dyDescent="0.2">
       <c r="L19"/>
       <c r="M19"/>
     </row>
-    <row r="20" spans="12:13">
+    <row r="20" spans="12:13" x14ac:dyDescent="0.2">
       <c r="L20"/>
       <c r="M20"/>
     </row>
-    <row r="21" spans="12:13">
+    <row r="21" spans="12:13" x14ac:dyDescent="0.2">
       <c r="L21"/>
       <c r="M21"/>
     </row>
-    <row r="22" spans="12:13">
+    <row r="22" spans="12:13" x14ac:dyDescent="0.2">
       <c r="L22"/>
       <c r="M22"/>
     </row>
-    <row r="23" spans="12:13">
+    <row r="23" spans="12:13" x14ac:dyDescent="0.2">
       <c r="L23"/>
       <c r="M23"/>
     </row>
-    <row r="24" spans="12:13">
+    <row r="24" spans="12:13" x14ac:dyDescent="0.2">
       <c r="L24"/>
       <c r="M24"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/PrivilegeCard.xlsx
+++ b/slots/resources/sample/PrivilegeCard.xlsx
@@ -101,12 +101,35 @@
         </r>
       </text>
     </comment>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1_1|2_2 ： 渠道1id_对应的商品id|渠道2id_对应的商品id
+注：1 =  google渠道ID；2 = apple 渠道ID</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
   <si>
     <t>序列ID</t>
   </si>
@@ -135,6 +158,9 @@
     <t>额外道具</t>
   </si>
   <si>
+    <t>渠道商品ID</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -144,6 +170,9 @@
     <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
+    <t>map&lt;int{_}String&gt;{|}</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -168,6 +197,9 @@
     <t>getItem</t>
   </si>
   <si>
+    <t>channelCommodity</t>
+  </si>
+  <si>
     <t>月卡</t>
   </si>
   <si>
@@ -177,25 +209,34 @@
     <t>1990000_415800</t>
   </si>
   <si>
+    <t>1_google499|2_ios499</t>
+  </si>
+  <si>
     <t>季卡</t>
   </si>
   <si>
-    <t>1990000_89970000</t>
-  </si>
-  <si>
-    <t>1990000_999700</t>
+    <t>1990000_74970000</t>
+  </si>
+  <si>
+    <t>1990000_833000</t>
+  </si>
+  <si>
+    <t>1_google2499|2_ios2499</t>
   </si>
   <si>
     <t>永久卡</t>
   </si>
   <si>
-    <t>1990000_454965000</t>
-  </si>
-  <si>
-    <t>1990000_1516600</t>
+    <t>1990000_349965000</t>
+  </si>
+  <si>
+    <t>1990000_1166600</t>
   </si>
   <si>
     <t>1031350_1</t>
+  </si>
+  <si>
+    <t>1_google9999|2_ios9999</t>
   </si>
 </sst>
 </file>
@@ -224,7 +265,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.25"/>
+      <color theme="0" tint="-0.249977111117893"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -379,12 +420,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -874,7 +915,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1237,7 +1278,7 @@
     <col min="7" max="7" width="18.875" style="1" customWidth="1"/>
     <col min="8" max="8" width="17.875" style="1" customWidth="1"/>
     <col min="9" max="9" width="23.625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.25" style="1"/>
+    <col min="10" max="10" width="25.75" style="1" customWidth="1"/>
     <col min="11" max="11" width="9" style="1"/>
     <col min="12" max="12" width="7.875" style="1" customWidth="1"/>
     <col min="13" max="13" width="26.75" style="1" customWidth="1"/>
@@ -1246,7 +1287,7 @@
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1274,59 +1315,68 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>12</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1340,7 +1390,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:10">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1348,7 +1398,7 @@
         <v>56001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -1360,10 +1410,13 @@
         <v>4.99</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -1374,7 +1427,7 @@
         <v>56002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
@@ -1383,13 +1436,16 @@
         <v>90</v>
       </c>
       <c r="F6" s="1">
-        <v>29.99</v>
+        <v>24.99</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="L6"/>
       <c r="M6"/>
@@ -1402,7 +1458,7 @@
         <v>56003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -1414,13 +1470,16 @@
         <v>99.99</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="L7"/>
       <c r="M7"/>

--- a/slots/resources/sample/PrivilegeCard.xlsx
+++ b/slots/resources/sample/PrivilegeCard.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\java\gamedoc\游戏配置表\activity\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE1D610-3E83-4D34-A1A7-CA4F8E5DDD73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="PrivilegeCard" sheetId="1" r:id="rId1"/>
@@ -33,12 +27,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -62,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -85,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -107,12 +101,35 @@
         </r>
       </text>
     </comment>
+    <comment ref="J1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1_1|2_2 ： 渠道1id_对应的商品id|渠道2id_对应的商品id
+注：1 =  google渠道ID；2 = apple 渠道ID</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
   <si>
     <t>序列ID</t>
   </si>
@@ -141,6 +158,9 @@
     <t>额外道具</t>
   </si>
   <si>
+    <t>渠道商品ID</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -150,6 +170,9 @@
     <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
+    <t>map&lt;int{_}String&gt;{|}</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -174,6 +197,9 @@
     <t>getItem</t>
   </si>
   <si>
+    <t>channelCommodity</t>
+  </si>
+  <si>
     <t>月卡</t>
   </si>
   <si>
@@ -183,13 +209,19 @@
     <t>1990000_415800</t>
   </si>
   <si>
+    <t>1_google499|2_ios499</t>
+  </si>
+  <si>
     <t>季卡</t>
   </si>
   <si>
-    <t>1990000_89970000</t>
-  </si>
-  <si>
-    <t>1990000_999700</t>
+    <t>1990000_74970000</t>
+  </si>
+  <si>
+    <t>1990000_833000</t>
+  </si>
+  <si>
+    <t>1_google2499|2_ios2499</t>
   </si>
   <si>
     <t>永久卡</t>
@@ -204,23 +236,20 @@
     <t>1031350_1</t>
   </si>
   <si>
-    <t>渠道商品ID</t>
-  </si>
-  <si>
-    <t>map&lt;int{_}String&gt;{|}</t>
-  </si>
-  <si>
-    <t>channelCommodity</t>
-  </si>
-  <si>
-    <t>1_1|2_2</t>
+    <t>1_google9999|2_ios9999</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,6 +274,150 @@
       <color indexed="8"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -257,14 +430,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -273,7 +440,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -283,8 +450,188 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -307,9 +654,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -339,17 +928,61 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -627,14 +1260,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:M24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="9.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.25" style="1" customWidth="1"/>
@@ -645,7 +1278,7 @@
     <col min="7" max="7" width="18.875" style="1" customWidth="1"/>
     <col min="8" max="8" width="17.875" style="1" customWidth="1"/>
     <col min="9" max="9" width="23.625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="21.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.75" style="1" customWidth="1"/>
     <col min="11" max="11" width="9" style="1"/>
     <col min="12" max="12" width="7.875" style="1" customWidth="1"/>
     <col min="13" max="13" width="26.75" style="1" customWidth="1"/>
@@ -654,7 +1287,7 @@
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -683,70 +1316,70 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -757,7 +1390,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -765,7 +1398,7 @@
         <v>56001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -777,16 +1410,16 @@
         <v>4.99</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -794,7 +1427,7 @@
         <v>56002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
@@ -803,21 +1436,21 @@
         <v>90</v>
       </c>
       <c r="F6" s="1">
-        <v>29.99</v>
+        <v>24.99</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="L6"/>
       <c r="M6"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -825,7 +1458,7 @@
         <v>56003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -837,91 +1470,91 @@
         <v>99.99</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L7"/>
       <c r="M7"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="12:13">
       <c r="L8"/>
       <c r="M8"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="12:13">
       <c r="L9"/>
       <c r="M9"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="12:13">
       <c r="L10"/>
       <c r="M10"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="12:13">
       <c r="L11"/>
       <c r="M11"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="12:13">
       <c r="L12"/>
       <c r="M12"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="12:13">
       <c r="L13"/>
       <c r="M13"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="12:13">
       <c r="L14"/>
       <c r="M14"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="12:13">
       <c r="L15"/>
       <c r="M15"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="12:13">
       <c r="L16"/>
       <c r="M16"/>
     </row>
-    <row r="17" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="12:13">
       <c r="L17"/>
       <c r="M17"/>
     </row>
-    <row r="18" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="12:13">
       <c r="L18"/>
       <c r="M18"/>
     </row>
-    <row r="19" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="12:13">
       <c r="L19"/>
       <c r="M19"/>
     </row>
-    <row r="20" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="12:13">
       <c r="L20"/>
       <c r="M20"/>
     </row>
-    <row r="21" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="12:13">
       <c r="L21"/>
       <c r="M21"/>
     </row>
-    <row r="22" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="12:13">
       <c r="L22"/>
       <c r="M22"/>
     </row>
-    <row r="23" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="12:13">
       <c r="L23"/>
       <c r="M23"/>
     </row>
-    <row r="24" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="12:13">
       <c r="L24"/>
       <c r="M24"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/PrivilegeCard.xlsx
+++ b/slots/resources/sample/PrivilegeCard.xlsx
@@ -203,40 +203,40 @@
     <t>月卡</t>
   </si>
   <si>
-    <t>1990000_12475000</t>
-  </si>
-  <si>
-    <t>1990000_415800</t>
+    <t>1990000_34825000</t>
+  </si>
+  <si>
+    <t>1990000_1160800</t>
+  </si>
+  <si>
+    <t>1_google199|2_ios199</t>
+  </si>
+  <si>
+    <t>季卡</t>
+  </si>
+  <si>
+    <t>1990000_104790000</t>
+  </si>
+  <si>
+    <t>1990000_1164300</t>
   </si>
   <si>
     <t>1_google499|2_ios499</t>
   </si>
   <si>
-    <t>季卡</t>
-  </si>
-  <si>
-    <t>1990000_74970000</t>
-  </si>
-  <si>
-    <t>1990000_833000</t>
-  </si>
-  <si>
-    <t>1_google2499|2_ios2499</t>
-  </si>
-  <si>
     <t>永久卡</t>
   </si>
   <si>
-    <t>1990000_349965000</t>
-  </si>
-  <si>
-    <t>1990000_1166600</t>
+    <t>1990000_489755000</t>
+  </si>
+  <si>
+    <t>1990000_1632500</t>
   </si>
   <si>
     <t>1031350_1</t>
   </si>
   <si>
-    <t>1_google9999|2_ios9999</t>
+    <t>1_google1999|2_ios1999</t>
   </si>
 </sst>
 </file>
@@ -1407,7 +1407,7 @@
         <v>30</v>
       </c>
       <c r="F5" s="1">
-        <v>4.99</v>
+        <v>1.99</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>24</v>
@@ -1436,7 +1436,7 @@
         <v>90</v>
       </c>
       <c r="F6" s="1">
-        <v>24.99</v>
+        <v>4.99</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>28</v>
@@ -1467,7 +1467,7 @@
         <v>999999</v>
       </c>
       <c r="F7" s="1">
-        <v>99.99</v>
+        <v>19.99</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>32</v>

--- a/slots/resources/sample/PrivilegeCard.xlsx
+++ b/slots/resources/sample/PrivilegeCard.xlsx
@@ -215,13 +215,13 @@
     <t>季卡</t>
   </si>
   <si>
-    <t>1990000_104790000</t>
-  </si>
-  <si>
-    <t>1990000_1164300</t>
-  </si>
-  <si>
-    <t>1_google499|2_ios499</t>
+    <t>1990000_125790000</t>
+  </si>
+  <si>
+    <t>1990000_1397700</t>
+  </si>
+  <si>
+    <t>1_google599|2_ios599</t>
   </si>
   <si>
     <t>永久卡</t>
@@ -265,13 +265,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0" tint="-0.249977111117893"/>
+      <color indexed="8"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <color indexed="8"/>
+      <color theme="0" tint="-0.249977111117893"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -918,14 +918,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1276,7 +1276,7 @@
     <col min="5" max="5" width="8.875" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.375" style="1" customWidth="1"/>
     <col min="7" max="7" width="18.875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20" style="1" customWidth="1"/>
     <col min="9" max="9" width="23.625" style="1" customWidth="1"/>
     <col min="10" max="10" width="25.75" style="1" customWidth="1"/>
     <col min="11" max="11" width="9" style="1"/>
@@ -1287,7 +1287,7 @@
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1319,7 +1319,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:13">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:13">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -1372,14 +1372,14 @@
       <c r="H3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="5" t="s">
         <v>21</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:13">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1390,7 +1390,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:13">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -1409,10 +1409,10 @@
       <c r="F5" s="1">
         <v>1.99</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J5" s="1" t="s">
@@ -1436,12 +1436,12 @@
         <v>90</v>
       </c>
       <c r="F6" s="1">
-        <v>4.99</v>
-      </c>
-      <c r="G6" s="5" t="s">
+        <v>5.99</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="6" t="s">
         <v>29</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -1469,10 +1469,10 @@
       <c r="F7" s="1">
         <v>19.99</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="6" t="s">
         <v>33</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -1484,39 +1484,39 @@
       <c r="L7"/>
       <c r="M7"/>
     </row>
-    <row r="8" spans="12:13">
+    <row r="8" spans="1:13">
       <c r="L8"/>
       <c r="M8"/>
     </row>
-    <row r="9" spans="12:13">
+    <row r="9" spans="1:13">
       <c r="L9"/>
       <c r="M9"/>
     </row>
-    <row r="10" spans="12:13">
+    <row r="10" spans="1:13">
       <c r="L10"/>
       <c r="M10"/>
     </row>
-    <row r="11" spans="12:13">
+    <row r="11" spans="1:13">
       <c r="L11"/>
       <c r="M11"/>
     </row>
-    <row r="12" spans="12:13">
+    <row r="12" spans="1:13">
       <c r="L12"/>
       <c r="M12"/>
     </row>
-    <row r="13" spans="12:13">
+    <row r="13" spans="1:13">
       <c r="L13"/>
       <c r="M13"/>
     </row>
-    <row r="14" spans="12:13">
+    <row r="14" spans="1:13">
       <c r="L14"/>
       <c r="M14"/>
     </row>
-    <row r="15" spans="12:13">
+    <row r="15" spans="1:13">
       <c r="L15"/>
       <c r="M15"/>
     </row>
-    <row r="16" spans="12:13">
+    <row r="16" spans="1:13">
       <c r="L16"/>
       <c r="M16"/>
     </row>

--- a/slots/resources/sample/PrivilegeCard.xlsx
+++ b/slots/resources/sample/PrivilegeCard.xlsx
@@ -203,10 +203,10 @@
     <t>月卡</t>
   </si>
   <si>
-    <t>1990000_34825000</t>
-  </si>
-  <si>
-    <t>1990000_1160800</t>
+    <t>1990000_16716000</t>
+  </si>
+  <si>
+    <t>1990000_557200</t>
   </si>
   <si>
     <t>1_google199|2_ios199</t>
@@ -215,10 +215,10 @@
     <t>季卡</t>
   </si>
   <si>
-    <t>1990000_125790000</t>
-  </si>
-  <si>
-    <t>1990000_1397700</t>
+    <t>1990000_62895000</t>
+  </si>
+  <si>
+    <t>1990000_698800</t>
   </si>
   <si>
     <t>1_google599|2_ios599</t>
@@ -227,10 +227,10 @@
     <t>永久卡</t>
   </si>
   <si>
-    <t>1990000_489755000</t>
-  </si>
-  <si>
-    <t>1990000_1632500</t>
+    <t>1990000_251874000</t>
+  </si>
+  <si>
+    <t>1990000_839600</t>
   </si>
   <si>
     <t>1031350_1</t>

--- a/slots/resources/sample/PrivilegeCard.xlsx
+++ b/slots/resources/sample/PrivilegeCard.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="PrivilegeCard" sheetId="1" r:id="rId1"/>
@@ -203,34 +203,34 @@
     <t>月卡</t>
   </si>
   <si>
-    <t>1990000_16716000</t>
-  </si>
-  <si>
-    <t>1990000_557200</t>
-  </si>
-  <si>
-    <t>1_google199|2_ios199</t>
+    <t>1990000_356400</t>
+  </si>
+  <si>
+    <t>1990000_11900</t>
+  </si>
+  <si>
+    <t>1_google99|2_ios99</t>
   </si>
   <si>
     <t>季卡</t>
   </si>
   <si>
-    <t>1990000_62895000</t>
-  </si>
-  <si>
-    <t>1990000_698800</t>
-  </si>
-  <si>
-    <t>1_google599|2_ios599</t>
+    <t>1990000_2245500</t>
+  </si>
+  <si>
+    <t>1990000_25000</t>
+  </si>
+  <si>
+    <t>1_google499|2_ios499</t>
   </si>
   <si>
     <t>永久卡</t>
   </si>
   <si>
-    <t>1990000_251874000</t>
-  </si>
-  <si>
-    <t>1990000_839600</t>
+    <t>1990000_10794600</t>
+  </si>
+  <si>
+    <t>1990000_60000</t>
   </si>
   <si>
     <t>1031350_1</t>
@@ -1407,7 +1407,7 @@
         <v>30</v>
       </c>
       <c r="F5" s="1">
-        <v>1.99</v>
+        <v>0.99</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>24</v>
@@ -1436,7 +1436,7 @@
         <v>90</v>
       </c>
       <c r="F6" s="1">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>28</v>

--- a/slots/resources/sample/PrivilegeCard.xlsx
+++ b/slots/resources/sample/PrivilegeCard.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="PrivilegeCard" sheetId="1" r:id="rId1"/>
@@ -203,34 +203,34 @@
     <t>月卡</t>
   </si>
   <si>
-    <t>1990000_356400</t>
-  </si>
-  <si>
-    <t>1990000_11900</t>
-  </si>
-  <si>
-    <t>1_google99|2_ios99</t>
+    <t>1990000_16716000</t>
+  </si>
+  <si>
+    <t>1990000_557200</t>
+  </si>
+  <si>
+    <t>1_google199|2_ios199</t>
   </si>
   <si>
     <t>季卡</t>
   </si>
   <si>
-    <t>1990000_2245500</t>
-  </si>
-  <si>
-    <t>1990000_25000</t>
-  </si>
-  <si>
-    <t>1_google499|2_ios499</t>
+    <t>1990000_62895000</t>
+  </si>
+  <si>
+    <t>1990000_698800</t>
+  </si>
+  <si>
+    <t>1_google599|2_ios599</t>
   </si>
   <si>
     <t>永久卡</t>
   </si>
   <si>
-    <t>1990000_10794600</t>
-  </si>
-  <si>
-    <t>1990000_60000</t>
+    <t>1990000_251874000</t>
+  </si>
+  <si>
+    <t>1990000_839600</t>
   </si>
   <si>
     <t>1031350_1</t>
@@ -1407,7 +1407,7 @@
         <v>30</v>
       </c>
       <c r="F5" s="1">
-        <v>0.99</v>
+        <v>1.99</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>24</v>
@@ -1436,7 +1436,7 @@
         <v>90</v>
       </c>
       <c r="F6" s="1">
-        <v>4.99</v>
+        <v>5.99</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>28</v>

--- a/slots/resources/sample/PrivilegeCard.xlsx
+++ b/slots/resources/sample/PrivilegeCard.xlsx
@@ -203,10 +203,10 @@
     <t>月卡</t>
   </si>
   <si>
-    <t>1990000_356400</t>
-  </si>
-  <si>
-    <t>1990000_11900</t>
+    <t>1990000_1069200</t>
+  </si>
+  <si>
+    <t>1990000_35600</t>
   </si>
   <si>
     <t>1_google99|2_ios99</t>
@@ -215,10 +215,10 @@
     <t>季卡</t>
   </si>
   <si>
-    <t>1990000_2245500</t>
-  </si>
-  <si>
-    <t>1990000_25000</t>
+    <t>1990000_6736500</t>
+  </si>
+  <si>
+    <t>1990000_74900</t>
   </si>
   <si>
     <t>1_google499|2_ios499</t>
@@ -227,10 +227,10 @@
     <t>永久卡</t>
   </si>
   <si>
-    <t>1990000_10794600</t>
-  </si>
-  <si>
-    <t>1990000_60000</t>
+    <t>1990000_38980500</t>
+  </si>
+  <si>
+    <t>1990000_216600</t>
   </si>
   <si>
     <t>1031350_1</t>

--- a/slots/resources/sample/PrivilegeCard.xlsx
+++ b/slots/resources/sample/PrivilegeCard.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="PrivilegeCard" sheetId="1" r:id="rId1"/>
@@ -203,34 +203,34 @@
     <t>月卡</t>
   </si>
   <si>
-    <t>1990000_16716000</t>
-  </si>
-  <si>
-    <t>1990000_557200</t>
-  </si>
-  <si>
-    <t>1_google199|2_ios199</t>
+    <t>1990000_1069200</t>
+  </si>
+  <si>
+    <t>1990000_35600</t>
+  </si>
+  <si>
+    <t>1_google99|2_ios99</t>
   </si>
   <si>
     <t>季卡</t>
   </si>
   <si>
-    <t>1990000_62895000</t>
-  </si>
-  <si>
-    <t>1990000_698800</t>
-  </si>
-  <si>
-    <t>1_google599|2_ios599</t>
+    <t>1990000_6736500</t>
+  </si>
+  <si>
+    <t>1990000_74900</t>
+  </si>
+  <si>
+    <t>1_google499|2_ios499</t>
   </si>
   <si>
     <t>永久卡</t>
   </si>
   <si>
-    <t>1990000_251874000</t>
-  </si>
-  <si>
-    <t>1990000_839600</t>
+    <t>1990000_38980500</t>
+  </si>
+  <si>
+    <t>1990000_216600</t>
   </si>
   <si>
     <t>1031350_1</t>
@@ -1407,7 +1407,7 @@
         <v>30</v>
       </c>
       <c r="F5" s="1">
-        <v>1.99</v>
+        <v>0.99</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>24</v>
@@ -1436,7 +1436,7 @@
         <v>90</v>
       </c>
       <c r="F6" s="1">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>28</v>
